--- a/references/DataDictionary042022.xlsx
+++ b/references/DataDictionary042022.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/mcburton_pitt_edu/Documents/teaching/cmpinf2910 - Case Studies in Data Science/injury-data/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ananddivakaran/Documents/Anand/MDS/cpsa/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC42628-3AA2-4D53-8D55-04A2801C1F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5367AD60-C4D3-3A44-BAA6-B97FC3A79D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="500" windowWidth="12440" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="620" windowWidth="19980" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2018 and prior" sheetId="1" r:id="rId1"/>
     <sheet name="2019 and beyond" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Table2[#All]</definedName>
@@ -22,18 +23,28 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'2018 and prior'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2019 and beyond'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="174">
   <si>
     <t>CPSC_Case_Number</t>
   </si>
@@ -537,13 +548,31 @@
   </si>
   <si>
     <t>3 - Non-Binary/Other (NA before 2021)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disposition Code </t>
+  </si>
+  <si>
+    <t>Hospitalized?</t>
+  </si>
+  <si>
+    <t>4,2,5,8</t>
+  </si>
+  <si>
+    <t>1,6,9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,13 +580,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -572,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -583,11 +630,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -619,6 +706,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description/Code book"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{30A583C0-F31F-8346-827C-F606E2F33BF5}" name="Table4" displayName="Table4" ref="C10:D12" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="C10:D12" xr:uid="{30A583C0-F31F-8346-827C-F606E2F33BF5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{E99FD5B6-1179-4C46-A81C-82E98593DF7C}" name="Disposition Code " dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C55C9429-8166-BB49-A56C-7671A307D013}" name="Hospitalized?" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1740,7 +1838,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
@@ -1907,7 +2005,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B53" t="s">
@@ -2079,7 +2177,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="A85" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B85" t="s">
@@ -2101,7 +2199,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -2245,7 +2343,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+      <c r="A111" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B111" t="s">
@@ -2266,7 +2364,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="A114" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B114" t="s">
@@ -2309,7 +2407,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="A119" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B119" t="s">
@@ -2370,4 +2468,172 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E98B430-EB76-AB47-8AF7-1FC68F0EC1A4}">
+  <dimension ref="B4:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="7"/>
+    <col min="3" max="3" width="16.6640625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="6"/>
+      <c r="C12" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="23" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="F23" s="8">
+        <v>5283928</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="F24" s="8">
+        <v>38706</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F25" s="7">
+        <f>SUM(F23:F24)</f>
+        <v>5322634</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>